--- a/final_data_pipeline/output/325212longform.xlsx
+++ b/final_data_pipeline/output/325212longform.xlsx
@@ -789,7 +789,7 @@
         <v>73</v>
       </c>
       <c r="AA2">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB2">
         <v>8000</v>
@@ -878,7 +878,7 @@
         <v>73</v>
       </c>
       <c r="AA3">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB3">
         <v>8000</v>
@@ -967,7 +967,7 @@
         <v>73</v>
       </c>
       <c r="AA4">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB4">
         <v>8000</v>
@@ -1056,7 +1056,7 @@
         <v>73</v>
       </c>
       <c r="AA5">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB5">
         <v>8000</v>
@@ -1145,7 +1145,7 @@
         <v>73</v>
       </c>
       <c r="AA6">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB6">
         <v>8000</v>
@@ -1234,7 +1234,7 @@
         <v>73</v>
       </c>
       <c r="AA7">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB7">
         <v>8000</v>
@@ -1323,7 +1323,7 @@
         <v>73</v>
       </c>
       <c r="AA8">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB8">
         <v>8000</v>
@@ -1412,7 +1412,7 @@
         <v>73</v>
       </c>
       <c r="AA9">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB9">
         <v>8000</v>
@@ -1501,7 +1501,7 @@
         <v>73</v>
       </c>
       <c r="AA10">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB10">
         <v>8000</v>
@@ -1590,7 +1590,7 @@
         <v>73</v>
       </c>
       <c r="AA11">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB11">
         <v>8000</v>
@@ -1679,7 +1679,7 @@
         <v>73</v>
       </c>
       <c r="AA12">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB12">
         <v>8000</v>
@@ -1768,7 +1768,7 @@
         <v>73</v>
       </c>
       <c r="AA13">
-        <v>10</v>
+        <v>21.28240740740739</v>
       </c>
       <c r="AB13">
         <v>8000</v>
@@ -3993,7 +3993,7 @@
         <v>73</v>
       </c>
       <c r="AA38">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB38">
         <v>8000</v>
@@ -4082,7 +4082,7 @@
         <v>73</v>
       </c>
       <c r="AA39">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB39">
         <v>8000</v>
@@ -4171,7 +4171,7 @@
         <v>73</v>
       </c>
       <c r="AA40">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB40">
         <v>8000</v>
@@ -4260,7 +4260,7 @@
         <v>73</v>
       </c>
       <c r="AA41">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB41">
         <v>8000</v>
@@ -4349,7 +4349,7 @@
         <v>73</v>
       </c>
       <c r="AA42">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB42">
         <v>8000</v>
@@ -4438,7 +4438,7 @@
         <v>73</v>
       </c>
       <c r="AA43">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB43">
         <v>8000</v>
@@ -4527,7 +4527,7 @@
         <v>73</v>
       </c>
       <c r="AA44">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB44">
         <v>8000</v>
@@ -4616,7 +4616,7 @@
         <v>73</v>
       </c>
       <c r="AA45">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB45">
         <v>8000</v>
@@ -4705,7 +4705,7 @@
         <v>73</v>
       </c>
       <c r="AA46">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB46">
         <v>8000</v>
@@ -4794,7 +4794,7 @@
         <v>73</v>
       </c>
       <c r="AA47">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB47">
         <v>8000</v>
@@ -4883,7 +4883,7 @@
         <v>73</v>
       </c>
       <c r="AA48">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB48">
         <v>8000</v>
@@ -4972,7 +4972,7 @@
         <v>73</v>
       </c>
       <c r="AA49">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB49">
         <v>8000</v>
@@ -5061,7 +5061,7 @@
         <v>73</v>
       </c>
       <c r="AA50">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB50">
         <v>8000</v>
@@ -5150,7 +5150,7 @@
         <v>73</v>
       </c>
       <c r="AA51">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB51">
         <v>8000</v>
@@ -5239,7 +5239,7 @@
         <v>73</v>
       </c>
       <c r="AA52">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB52">
         <v>8000</v>
@@ -5328,7 +5328,7 @@
         <v>73</v>
       </c>
       <c r="AA53">
-        <v>10</v>
+        <v>13.75752314814816</v>
       </c>
       <c r="AB53">
         <v>8000</v>
@@ -6841,7 +6841,7 @@
         <v>73</v>
       </c>
       <c r="AA70">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB70">
         <v>8000</v>
@@ -6930,7 +6930,7 @@
         <v>73</v>
       </c>
       <c r="AA71">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB71">
         <v>8000</v>
@@ -7019,7 +7019,7 @@
         <v>73</v>
       </c>
       <c r="AA72">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB72">
         <v>8000</v>
@@ -7108,7 +7108,7 @@
         <v>73</v>
       </c>
       <c r="AA73">
-        <v>10</v>
+        <v>19.65277777777778</v>
       </c>
       <c r="AB73">
         <v>8000</v>
